--- a/Brooklyn_Nets_2025-26_stats.xlsx
+++ b/Brooklyn_Nets_2025-26_stats.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1185,6 +1185,66 @@
         <v>2</v>
       </c>
       <c r="R12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ORL</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>15</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" t="n">
+        <v>8</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>12</v>
+      </c>
+      <c r="K13" t="n">
+        <v>24</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4</v>
+      </c>
+      <c r="M13" t="n">
+        <v>12</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1199,7 +1259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1951,6 +2011,66 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ORL</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>7</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1965,7 +2085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2717,6 +2837,66 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ORL</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>11</v>
+      </c>
+      <c r="L13" t="n">
+        <v>5</v>
+      </c>
+      <c r="M13" t="n">
+        <v>4</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2731,7 +2911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3483,6 +3663,66 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ORL</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3519,7 +3759,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23.1</v>
+        <v>23.18181818181818</v>
       </c>
     </row>
     <row r="3">
@@ -3539,7 +3779,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15.18181818181818</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -3549,7 +3789,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.727272727272727</v>
+        <v>9.916666666666666</v>
       </c>
     </row>
     <row r="6">
@@ -3559,7 +3799,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.111111111111111</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -3569,7 +3809,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="8">
@@ -3579,27 +3819,27 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.1</v>
+        <v>7.181818181818182</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Day'Ron Sharpe</t>
+          <t>Jalen Wilson</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Jalen Wilson</t>
+          <t>Day'Ron Sharpe</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.5</v>
+        <v>6.454545454545454</v>
       </c>
     </row>
     <row r="11">
@@ -3609,7 +3849,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.454545454545454</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="12">
@@ -3619,7 +3859,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6.2</v>
+        <v>6.166666666666667</v>
       </c>
     </row>
     <row r="13">
@@ -3705,47 +3945,47 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.727272727272727</v>
+        <v>3.666666666666667</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Terance Mann</t>
+          <t>Egor Dëmin</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.454545454545455</v>
+        <v>3.181818181818182</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Egor Dëmin</t>
+          <t>Terance Mann</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.3</v>
+        <v>3.166666666666667</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cam Thomas</t>
+          <t>Michael Porter Jr.</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.625</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Michael Porter Jr.</t>
+          <t>Cam Thomas</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.6</v>
+        <v>2.625</v>
       </c>
     </row>
     <row r="7">
@@ -3765,7 +4005,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.363636363636364</v>
+        <v>2.333333333333333</v>
       </c>
     </row>
     <row r="9">
@@ -3775,7 +4015,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -3785,7 +4025,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.727272727272727</v>
+        <v>1.833333333333333</v>
       </c>
     </row>
     <row r="11">
@@ -3795,7 +4035,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.7</v>
+        <v>1.818181818181818</v>
       </c>
     </row>
     <row r="12">
@@ -3835,7 +4075,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="16">
@@ -3891,7 +4131,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.4</v>
+        <v>7.727272727272728</v>
       </c>
     </row>
     <row r="3">
@@ -3901,7 +4141,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.090909090909091</v>
+        <v>6.916666666666667</v>
       </c>
     </row>
     <row r="4">
@@ -3911,7 +4151,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.3</v>
+        <v>5.272727272727272</v>
       </c>
     </row>
     <row r="5">
@@ -3921,7 +4161,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.909090909090909</v>
+        <v>3.916666666666667</v>
       </c>
     </row>
     <row r="6">
@@ -3931,7 +4171,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.363636363636364</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="7">
@@ -3941,7 +4181,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.2</v>
+        <v>3.181818181818182</v>
       </c>
     </row>
     <row r="8">
@@ -3951,7 +4191,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="9">
@@ -3961,27 +4201,27 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.555555555555555</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ben Saraf</t>
+          <t>Drake Powell</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.857142857142857</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Drake Powell</t>
+          <t>Ben Saraf</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.8</v>
+        <v>1.857142857142857</v>
       </c>
     </row>
     <row r="12">
@@ -4077,7 +4317,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.1</v>
+        <v>3.090909090909091</v>
       </c>
     </row>
     <row r="3">
@@ -4093,7 +4333,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Egor Dëmin</t>
+          <t>Ziaire Williams</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -4103,17 +4343,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ziaire Williams</t>
+          <t>Egor Dëmin</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.777777777777778</v>
+        <v>1.727272727272727</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jalen Wilson</t>
+          <t>Noah Clowney</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -4123,11 +4363,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Noah Clowney</t>
+          <t>Jalen Wilson</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.454545454545455</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="8">
@@ -4137,27 +4377,27 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.272727272727273</v>
+        <v>1.166666666666667</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Drake Powell</t>
+          <t>Terance Mann</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>1.083333333333333</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Terance Mann</t>
+          <t>Drake Powell</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="11">
@@ -4197,7 +4437,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3</v>
+        <v>0.2727272727272727</v>
       </c>
     </row>
     <row r="15">
@@ -4241,7 +4481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4502,6 +4742,27 @@
         <v>228</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ORL</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>98</v>
+      </c>
+      <c r="D13" t="n">
+        <v>105</v>
+      </c>
+      <c r="E13" t="n">
+        <v>203</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
